--- a/outputs/v0/05_large_output.xlsx
+++ b/outputs/v0/05_large_output.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Stats" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Stats" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment Stats" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z-Scores" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,65 +427,105 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>test1</t>
+          <t>quiz_1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>test2</t>
+          <t>quiz_2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>test3</t>
+          <t>quiz_3</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>test4</t>
+          <t>quiz_4</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>test5</t>
+          <t>test_1</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>test_2</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>test_3</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>test_4</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_5</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>test_6</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>simple_average</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>weighted_average</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>letter_grade</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>slope</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>std_dev</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>highest_score</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>lowest_score</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>percentile</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>z_score</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>above_class_average</t>
         </is>
@@ -497,45 +538,69 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D2" t="n">
+        <v>52</v>
+      </c>
+      <c r="E2" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2" t="n">
+        <v>82</v>
+      </c>
+      <c r="G2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I2" t="n">
         <v>78</v>
       </c>
-      <c r="E2" t="n">
-        <v>74</v>
-      </c>
-      <c r="F2" t="n">
-        <v>80</v>
-      </c>
-      <c r="G2" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>71</v>
+      </c>
+      <c r="K2" t="n">
+        <v>71</v>
+      </c>
+      <c r="L2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="M2" t="n">
+        <v>73.283333</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.193744</v>
-      </c>
-      <c r="K2" t="n">
-        <v>80</v>
-      </c>
-      <c r="L2" t="n">
-        <v>72</v>
-      </c>
-      <c r="M2" t="n">
-        <v>15</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
+      <c r="O2" t="n">
+        <v>0.345455</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10.660936</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>92</v>
+      </c>
+      <c r="R2" t="n">
+        <v>52</v>
+      </c>
+      <c r="S2" t="n">
+        <v>24</v>
+      </c>
+      <c r="T2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -545,45 +610,69 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C3" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>89</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
+        <v>66</v>
+      </c>
+      <c r="H3" t="n">
+        <v>69</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3</v>
+        <v>81</v>
       </c>
       <c r="J3" t="n">
-        <v>2.738613</v>
+        <v>72</v>
       </c>
       <c r="K3" t="n">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="L3" t="n">
-        <v>85</v>
+        <v>73.3</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
+        <v>71.65000000000001</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>-1.848485</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8.260346999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>84</v>
+      </c>
+      <c r="R3" t="n">
+        <v>56</v>
+      </c>
+      <c r="S3" t="n">
+        <v>31</v>
+      </c>
+      <c r="T3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -593,45 +682,69 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
+        <v>83</v>
+      </c>
+      <c r="D4" t="n">
+        <v>72</v>
+      </c>
+      <c r="E4" t="n">
+        <v>73</v>
+      </c>
+      <c r="F4" t="n">
+        <v>82</v>
+      </c>
+      <c r="G4" t="n">
+        <v>98</v>
+      </c>
+      <c r="H4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I4" t="n">
+        <v>92</v>
+      </c>
+      <c r="J4" t="n">
         <v>58</v>
       </c>
-      <c r="D4" t="n">
-        <v>64</v>
-      </c>
-      <c r="E4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F4" t="n">
-        <v>63</v>
-      </c>
-      <c r="G4" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>D-</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.387467</v>
-      </c>
       <c r="K4" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.121212</v>
+      </c>
+      <c r="P4" t="n">
+        <v>12.191071</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>98</v>
+      </c>
+      <c r="R4" t="n">
         <v>58</v>
       </c>
-      <c r="M4" t="n">
-        <v>20</v>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -641,44 +754,68 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C5" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D5" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>95</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>83</v>
+      </c>
+      <c r="H5" t="n">
+        <v>67</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>68</v>
       </c>
       <c r="J5" t="n">
-        <v>1.581139</v>
+        <v>81</v>
       </c>
       <c r="K5" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="L5" t="n">
-        <v>93</v>
+        <v>77.2</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="b">
+        <v>75.766667</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.09697</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11.458136</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>91</v>
+      </c>
+      <c r="R5" t="n">
+        <v>61</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -689,45 +826,69 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="G6" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
+        <v>83</v>
+      </c>
+      <c r="H6" t="n">
+        <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>63</v>
       </c>
       <c r="J6" t="n">
-        <v>2.701851</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>45</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>24</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
+        <v>85.45</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>2.745455</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14.775731</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>100</v>
+      </c>
+      <c r="R6" t="n">
+        <v>63</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -737,44 +898,68 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>94</v>
+      </c>
+      <c r="C7" t="n">
+        <v>85</v>
+      </c>
+      <c r="D7" t="n">
+        <v>67</v>
+      </c>
+      <c r="E7" t="n">
+        <v>87</v>
+      </c>
+      <c r="F7" t="n">
+        <v>68</v>
+      </c>
+      <c r="G7" t="n">
+        <v>74</v>
+      </c>
+      <c r="H7" t="n">
+        <v>70</v>
+      </c>
+      <c r="I7" t="n">
         <v>78</v>
       </c>
-      <c r="C7" t="n">
-        <v>80</v>
-      </c>
-      <c r="D7" t="n">
-        <v>76</v>
-      </c>
-      <c r="E7" t="n">
-        <v>82</v>
-      </c>
-      <c r="F7" t="n">
-        <v>79</v>
-      </c>
-      <c r="G7" t="n">
-        <v>79</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.4</v>
-      </c>
       <c r="J7" t="n">
-        <v>2.236068</v>
+        <v>91</v>
       </c>
       <c r="K7" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="L7" t="n">
-        <v>76</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>12</v>
-      </c>
-      <c r="N7" t="b">
+        <v>76.38333299999999</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>-1.157576</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10.418467</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>94</v>
+      </c>
+      <c r="R7" t="n">
+        <v>67</v>
+      </c>
+      <c r="S7" t="n">
+        <v>17</v>
+      </c>
+      <c r="T7" t="n">
+        <v>59</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -785,45 +970,69 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="D8" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+        <v>91</v>
+      </c>
+      <c r="H8" t="n">
+        <v>66</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>77</v>
       </c>
       <c r="J8" t="n">
-        <v>2.073644</v>
+        <v>58</v>
       </c>
       <c r="K8" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="L8" t="n">
-        <v>83</v>
+        <v>67.7</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
-      </c>
-      <c r="N8" t="b">
-        <v>1</v>
+        <v>69.683333</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>1.242424</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10.478019</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>91</v>
+      </c>
+      <c r="R8" t="n">
+        <v>58</v>
+      </c>
+      <c r="S8" t="n">
+        <v>35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -833,45 +1042,69 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>54</v>
+      </c>
+      <c r="C9" t="n">
         <v>67</v>
       </c>
-      <c r="C9" t="n">
-        <v>70</v>
-      </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
         <v>68</v>
       </c>
       <c r="F9" t="n">
+        <v>89</v>
+      </c>
+      <c r="G9" t="n">
+        <v>80</v>
+      </c>
+      <c r="H9" t="n">
         <v>72</v>
       </c>
-      <c r="G9" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>D+</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>66</v>
       </c>
       <c r="J9" t="n">
-        <v>2.701851</v>
+        <v>91</v>
       </c>
       <c r="K9" t="n">
         <v>72</v>
       </c>
       <c r="L9" t="n">
-        <v>65</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>17</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
+        <v>77.11666700000001</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0.987879</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13.931978</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
+        <v>54</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13</v>
+      </c>
+      <c r="T9" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -881,45 +1114,69 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C10" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D10" t="n">
+        <v>76</v>
+      </c>
+      <c r="E10" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" t="n">
+        <v>79</v>
+      </c>
+      <c r="G10" t="n">
+        <v>58</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>71</v>
+      </c>
+      <c r="J10" t="n">
+        <v>63</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83</v>
+      </c>
+      <c r="L10" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>71.666667</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.242424</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10.793517</v>
+      </c>
+      <c r="Q10" t="n">
         <v>93</v>
       </c>
-      <c r="E10" t="n">
-        <v>90</v>
-      </c>
-      <c r="F10" t="n">
-        <v>94</v>
-      </c>
-      <c r="G10" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.073644</v>
-      </c>
-      <c r="K10" t="n">
-        <v>94</v>
-      </c>
-      <c r="L10" t="n">
-        <v>89</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5</v>
-      </c>
-      <c r="N10" t="b">
-        <v>1</v>
+      <c r="R10" t="n">
+        <v>58</v>
+      </c>
+      <c r="S10" t="n">
+        <v>30</v>
+      </c>
+      <c r="T10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="V10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -929,44 +1186,68 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C11" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
         <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>69</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="J11" t="n">
-        <v>2.408319</v>
+        <v>60</v>
       </c>
       <c r="K11" t="n">
         <v>60</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>22</v>
-      </c>
-      <c r="N11" t="b">
+        <v>71.283333</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0.175758</v>
+      </c>
+      <c r="P11" t="n">
+        <v>15.021836</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>100</v>
+      </c>
+      <c r="R11" t="n">
+        <v>52</v>
+      </c>
+      <c r="S11" t="n">
+        <v>33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="V11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -977,44 +1258,68 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>52</v>
+      </c>
+      <c r="C12" t="n">
+        <v>75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>86</v>
+      </c>
+      <c r="E12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F12" t="n">
+        <v>92</v>
+      </c>
+      <c r="G12" t="n">
+        <v>77</v>
+      </c>
+      <c r="H12" t="n">
         <v>74</v>
       </c>
-      <c r="C12" t="n">
-        <v>77</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="I12" t="n">
+        <v>81</v>
+      </c>
+      <c r="J12" t="n">
         <v>80</v>
       </c>
-      <c r="E12" t="n">
-        <v>75</v>
-      </c>
-      <c r="F12" t="n">
-        <v>78</v>
-      </c>
-      <c r="G12" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.387467</v>
-      </c>
       <c r="K12" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="L12" t="n">
-        <v>74</v>
+        <v>77.7</v>
       </c>
       <c r="M12" t="n">
-        <v>14</v>
-      </c>
-      <c r="N12" t="b">
+        <v>79.933333</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>2.042424</v>
+      </c>
+      <c r="P12" t="n">
+        <v>11.274849</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>92</v>
+      </c>
+      <c r="R12" t="n">
+        <v>52</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1025,44 +1330,68 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>65</v>
+      </c>
+      <c r="C13" t="n">
+        <v>48</v>
+      </c>
+      <c r="D13" t="n">
+        <v>76</v>
+      </c>
+      <c r="E13" t="n">
+        <v>68</v>
+      </c>
+      <c r="F13" t="n">
+        <v>74</v>
+      </c>
+      <c r="G13" t="n">
+        <v>96</v>
+      </c>
+      <c r="H13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I13" t="n">
+        <v>84</v>
+      </c>
+      <c r="J13" t="n">
         <v>86</v>
       </c>
-      <c r="C13" t="n">
-        <v>84</v>
-      </c>
-      <c r="D13" t="n">
-        <v>89</v>
-      </c>
-      <c r="E13" t="n">
-        <v>87</v>
-      </c>
-      <c r="F13" t="n">
-        <v>90</v>
-      </c>
-      <c r="G13" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.387467</v>
-      </c>
       <c r="K13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L13" t="n">
-        <v>84</v>
+        <v>73.7</v>
       </c>
       <c r="M13" t="n">
-        <v>8</v>
-      </c>
-      <c r="N13" t="b">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>2.660606</v>
+      </c>
+      <c r="P13" t="n">
+        <v>13.968616</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>96</v>
+      </c>
+      <c r="R13" t="n">
+        <v>48</v>
+      </c>
+      <c r="S13" t="n">
+        <v>14</v>
+      </c>
+      <c r="T13" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="V13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1073,45 +1402,69 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="G14" t="n">
-        <v>64</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
+        <v>92</v>
+      </c>
+      <c r="H14" t="n">
+        <v>77</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4</v>
+        <v>95</v>
       </c>
       <c r="J14" t="n">
-        <v>2.236068</v>
+        <v>70</v>
       </c>
       <c r="K14" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L14" t="n">
-        <v>61</v>
+        <v>78.8</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
+        <v>79.15000000000001</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.763636</v>
+      </c>
+      <c r="P14" t="n">
+        <v>11.905181</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>95</v>
+      </c>
+      <c r="R14" t="n">
+        <v>60</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1121,45 +1474,69 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C15" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H15" t="n">
+        <v>85</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>97</v>
       </c>
       <c r="J15" t="n">
-        <v>2.387467</v>
+        <v>61</v>
       </c>
       <c r="K15" t="n">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="L15" t="n">
-        <v>90</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
-      </c>
-      <c r="N15" t="b">
-        <v>1</v>
+        <v>73.55</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0.69697</v>
+      </c>
+      <c r="P15" t="n">
+        <v>19.353151</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>22</v>
+      </c>
+      <c r="T15" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1169,45 +1546,69 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E16" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
+        <v>94</v>
+      </c>
+      <c r="H16" t="n">
+        <v>94</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>81</v>
       </c>
       <c r="J16" t="n">
-        <v>2.774887</v>
+        <v>74</v>
       </c>
       <c r="K16" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L16" t="n">
-        <v>48</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>23</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
+        <v>79.38333299999999</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0.387879</v>
+      </c>
+      <c r="P16" t="n">
+        <v>12.571573</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>94</v>
+      </c>
+      <c r="R16" t="n">
+        <v>58</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1217,45 +1618,69 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C17" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E17" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G17" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="H17" t="n">
+        <v>68</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>45</v>
       </c>
       <c r="J17" t="n">
-        <v>2.387467</v>
+        <v>80</v>
       </c>
       <c r="K17" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L17" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="M17" t="n">
-        <v>11</v>
-      </c>
-      <c r="N17" t="b">
-        <v>1</v>
+        <v>69.25</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>D+</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5333329999999999</v>
+      </c>
+      <c r="P17" t="n">
+        <v>12.797569</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>85</v>
+      </c>
+      <c r="R17" t="n">
+        <v>45</v>
+      </c>
+      <c r="S17" t="n">
+        <v>36</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1265,44 +1690,68 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
         <v>86</v>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="H18" t="n">
+        <v>84</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="J18" t="n">
-        <v>1.923538</v>
+        <v>63</v>
       </c>
       <c r="K18" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L18" t="n">
-        <v>84</v>
+        <v>81.7</v>
       </c>
       <c r="M18" t="n">
-        <v>9</v>
-      </c>
-      <c r="N18" t="b">
+        <v>81.266667</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.951515</v>
+      </c>
+      <c r="P18" t="n">
+        <v>14.360826</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>100</v>
+      </c>
+      <c r="R18" t="n">
+        <v>62</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1313,45 +1762,69 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C19" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D19" t="n">
+        <v>67</v>
+      </c>
+      <c r="E19" t="n">
+        <v>91</v>
+      </c>
+      <c r="F19" t="n">
+        <v>63</v>
+      </c>
+      <c r="G19" t="n">
+        <v>51</v>
+      </c>
+      <c r="H19" t="n">
+        <v>93</v>
+      </c>
+      <c r="I19" t="n">
         <v>68</v>
       </c>
-      <c r="E19" t="n">
-        <v>70</v>
-      </c>
-      <c r="F19" t="n">
-        <v>73</v>
-      </c>
-      <c r="G19" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.6</v>
-      </c>
       <c r="J19" t="n">
-        <v>2.073644</v>
+        <v>75</v>
       </c>
       <c r="K19" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="L19" t="n">
-        <v>68</v>
+        <v>76.8</v>
       </c>
       <c r="M19" t="n">
-        <v>16</v>
-      </c>
-      <c r="N19" t="b">
-        <v>0</v>
+        <v>75.816667</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0.787879</v>
+      </c>
+      <c r="P19" t="n">
+        <v>14.987402</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>99</v>
+      </c>
+      <c r="R19" t="n">
+        <v>51</v>
+      </c>
+      <c r="S19" t="n">
+        <v>19</v>
+      </c>
+      <c r="T19" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1361,44 +1834,68 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C20" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D20" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E20" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="F20" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>88</v>
+      </c>
+      <c r="H20" t="n">
+        <v>84</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>71</v>
       </c>
       <c r="J20" t="n">
-        <v>2.408319</v>
+        <v>45</v>
       </c>
       <c r="K20" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="L20" t="n">
-        <v>91</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" t="b">
+        <v>76.7</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>-2.212121</v>
+      </c>
+      <c r="P20" t="n">
+        <v>13.779615</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>89</v>
+      </c>
+      <c r="R20" t="n">
+        <v>45</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1409,44 +1906,68 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C21" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="F21" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G21" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="H21" t="n">
+        <v>55</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="J21" t="n">
-        <v>2.701851</v>
+        <v>75</v>
       </c>
       <c r="K21" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>21</v>
-      </c>
-      <c r="N21" t="b">
+        <v>71.05</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.5333329999999999</v>
+      </c>
+      <c r="P21" t="n">
+        <v>9.834180999999999</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>84</v>
+      </c>
+      <c r="R21" t="n">
+        <v>55</v>
+      </c>
+      <c r="S21" t="n">
+        <v>34</v>
+      </c>
+      <c r="T21" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="V21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1457,44 +1978,68 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F22" t="n">
         <v>77</v>
       </c>
       <c r="G22" t="n">
-        <v>77</v>
-      </c>
-      <c r="H22" t="inlineStr">
+        <v>86</v>
+      </c>
+      <c r="H22" t="n">
+        <v>67</v>
+      </c>
+      <c r="I22" t="n">
+        <v>84</v>
+      </c>
+      <c r="J22" t="n">
+        <v>82</v>
+      </c>
+      <c r="K22" t="n">
+        <v>75</v>
+      </c>
+      <c r="L22" t="n">
+        <v>78</v>
+      </c>
+      <c r="M22" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.236068</v>
-      </c>
-      <c r="K22" t="n">
-        <v>80</v>
-      </c>
-      <c r="L22" t="n">
-        <v>74</v>
-      </c>
-      <c r="M22" t="n">
-        <v>13</v>
-      </c>
-      <c r="N22" t="b">
+      <c r="O22" t="n">
+        <v>0.121212</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5.395471</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>86</v>
+      </c>
+      <c r="R22" t="n">
+        <v>67</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="V22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1505,45 +2050,69 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C23" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D23" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E23" t="n">
+        <v>62</v>
+      </c>
+      <c r="F23" t="n">
+        <v>75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>65</v>
+      </c>
+      <c r="I23" t="n">
+        <v>66</v>
+      </c>
+      <c r="J23" t="n">
+        <v>54</v>
+      </c>
+      <c r="K23" t="n">
+        <v>60</v>
+      </c>
+      <c r="L23" t="n">
+        <v>69</v>
+      </c>
+      <c r="M23" t="n">
+        <v>67.416667</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>D+</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>-2.072727</v>
+      </c>
+      <c r="P23" t="n">
+        <v>9.475114</v>
+      </c>
+      <c r="Q23" t="n">
         <v>85</v>
       </c>
-      <c r="F23" t="n">
-        <v>91</v>
-      </c>
-      <c r="G23" t="n">
-        <v>88</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.54951</v>
-      </c>
-      <c r="K23" t="n">
-        <v>91</v>
-      </c>
-      <c r="L23" t="n">
-        <v>85</v>
-      </c>
-      <c r="M23" t="n">
-        <v>7</v>
-      </c>
-      <c r="N23" t="b">
-        <v>1</v>
+      <c r="R23" t="n">
+        <v>54</v>
+      </c>
+      <c r="S23" t="n">
+        <v>38</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1553,44 +2122,68 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C24" t="n">
         <v>68</v>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="G24" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
+        <v>72</v>
+      </c>
+      <c r="H24" t="n">
+        <v>65</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4</v>
+        <v>65</v>
       </c>
       <c r="J24" t="n">
-        <v>2.701851</v>
+        <v>59</v>
       </c>
       <c r="K24" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L24" t="n">
-        <v>63</v>
+        <v>67.3</v>
       </c>
       <c r="M24" t="n">
-        <v>18</v>
-      </c>
-      <c r="N24" t="b">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>D+</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.175758</v>
+      </c>
+      <c r="P24" t="n">
+        <v>6.342975</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>79</v>
+      </c>
+      <c r="R24" t="n">
+        <v>57</v>
+      </c>
+      <c r="S24" t="n">
+        <v>37</v>
+      </c>
+      <c r="T24" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="V24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1601,44 +2194,68 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C25" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E25" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F25" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
+        <v>58</v>
+      </c>
+      <c r="H25" t="n">
+        <v>83</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>84</v>
       </c>
       <c r="J25" t="n">
-        <v>1.923538</v>
+        <v>80</v>
       </c>
       <c r="K25" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>94</v>
+        <v>85.7</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="b">
+        <v>84.933333</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0.224242</v>
+      </c>
+      <c r="P25" t="n">
+        <v>13.25854</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>100</v>
+      </c>
+      <c r="R25" t="n">
+        <v>58</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V25" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1649,44 +2266,1148 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="D26" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="E26" t="n">
+        <v>62</v>
+      </c>
+      <c r="F26" t="n">
+        <v>59</v>
+      </c>
+      <c r="G26" t="n">
+        <v>83</v>
+      </c>
+      <c r="H26" t="n">
+        <v>73</v>
+      </c>
+      <c r="I26" t="n">
+        <v>57</v>
+      </c>
+      <c r="J26" t="n">
+        <v>72</v>
+      </c>
+      <c r="K26" t="n">
+        <v>79</v>
+      </c>
+      <c r="L26" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>73</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>-2.224242</v>
+      </c>
+      <c r="P26" t="n">
+        <v>13.63207</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>100</v>
+      </c>
+      <c r="R26" t="n">
+        <v>57</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S026</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>86</v>
+      </c>
+      <c r="C27" t="n">
+        <v>74</v>
+      </c>
+      <c r="D27" t="n">
+        <v>72</v>
+      </c>
+      <c r="E27" t="n">
+        <v>75</v>
+      </c>
+      <c r="F27" t="n">
+        <v>76</v>
+      </c>
+      <c r="G27" t="n">
+        <v>59</v>
+      </c>
+      <c r="H27" t="n">
+        <v>85</v>
+      </c>
+      <c r="I27" t="n">
+        <v>100</v>
+      </c>
+      <c r="J27" t="n">
+        <v>85</v>
+      </c>
+      <c r="K27" t="n">
+        <v>55</v>
+      </c>
+      <c r="L27" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="M27" t="n">
+        <v>76.683333</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.29697</v>
+      </c>
+      <c r="P27" t="n">
+        <v>13.266918</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>100</v>
+      </c>
+      <c r="R27" t="n">
+        <v>55</v>
+      </c>
+      <c r="S27" t="n">
+        <v>16</v>
+      </c>
+      <c r="T27" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S027</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>76</v>
+      </c>
+      <c r="C28" t="n">
+        <v>54</v>
+      </c>
+      <c r="D28" t="n">
+        <v>53</v>
+      </c>
+      <c r="E28" t="n">
+        <v>83</v>
+      </c>
+      <c r="F28" t="n">
+        <v>75</v>
+      </c>
+      <c r="G28" t="n">
+        <v>65</v>
+      </c>
+      <c r="H28" t="n">
+        <v>47</v>
+      </c>
+      <c r="I28" t="n">
+        <v>58</v>
+      </c>
+      <c r="J28" t="n">
+        <v>76</v>
+      </c>
+      <c r="K28" t="n">
+        <v>74</v>
+      </c>
+      <c r="L28" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="M28" t="n">
+        <v>65.966667</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0.260606</v>
+      </c>
+      <c r="P28" t="n">
+        <v>12.350888</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>83</v>
+      </c>
+      <c r="R28" t="n">
+        <v>47</v>
+      </c>
+      <c r="S28" t="n">
+        <v>40</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S028</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>83</v>
+      </c>
+      <c r="C29" t="n">
+        <v>93</v>
+      </c>
+      <c r="D29" t="n">
+        <v>71</v>
+      </c>
+      <c r="E29" t="n">
+        <v>81</v>
+      </c>
+      <c r="F29" t="n">
+        <v>72</v>
+      </c>
+      <c r="G29" t="n">
+        <v>68</v>
+      </c>
+      <c r="H29" t="n">
+        <v>71</v>
+      </c>
+      <c r="I29" t="n">
+        <v>86</v>
+      </c>
+      <c r="J29" t="n">
+        <v>61</v>
+      </c>
+      <c r="K29" t="n">
+        <v>89</v>
+      </c>
+      <c r="L29" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>76</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.781818</v>
+      </c>
+      <c r="P29" t="n">
+        <v>10.352133</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>93</v>
+      </c>
+      <c r="R29" t="n">
+        <v>61</v>
+      </c>
+      <c r="S29" t="n">
+        <v>18</v>
+      </c>
+      <c r="T29" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S029</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>93</v>
+      </c>
+      <c r="C30" t="n">
+        <v>75</v>
+      </c>
+      <c r="D30" t="n">
+        <v>78</v>
+      </c>
+      <c r="E30" t="n">
+        <v>58</v>
+      </c>
+      <c r="F30" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" t="n">
+        <v>87</v>
+      </c>
+      <c r="H30" t="n">
+        <v>76</v>
+      </c>
+      <c r="I30" t="n">
+        <v>75</v>
+      </c>
+      <c r="J30" t="n">
+        <v>80</v>
+      </c>
+      <c r="K30" t="n">
+        <v>66</v>
+      </c>
+      <c r="L30" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>79.733333</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>-1.10303</v>
+      </c>
+      <c r="P30" t="n">
+        <v>12.263768</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>100</v>
+      </c>
+      <c r="R30" t="n">
+        <v>58</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S030</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>78</v>
+      </c>
+      <c r="C31" t="n">
+        <v>64</v>
+      </c>
+      <c r="D31" t="n">
+        <v>81</v>
+      </c>
+      <c r="E31" t="n">
+        <v>67</v>
+      </c>
+      <c r="F31" t="n">
+        <v>86</v>
+      </c>
+      <c r="G31" t="n">
+        <v>72</v>
+      </c>
+      <c r="H31" t="n">
+        <v>77</v>
+      </c>
+      <c r="I31" t="n">
+        <v>100</v>
+      </c>
+      <c r="J31" t="n">
+        <v>84</v>
+      </c>
+      <c r="K31" t="n">
+        <v>77</v>
+      </c>
+      <c r="L31" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="M31" t="n">
+        <v>80.63333299999999</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1.466667</v>
+      </c>
+      <c r="P31" t="n">
+        <v>10.243697</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>100</v>
+      </c>
+      <c r="R31" t="n">
+        <v>64</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S031</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>76</v>
+      </c>
+      <c r="C32" t="n">
+        <v>63</v>
+      </c>
+      <c r="D32" t="n">
+        <v>88</v>
+      </c>
+      <c r="E32" t="n">
+        <v>94</v>
+      </c>
+      <c r="F32" t="n">
+        <v>75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>96</v>
+      </c>
+      <c r="H32" t="n">
+        <v>73</v>
+      </c>
+      <c r="I32" t="n">
+        <v>51</v>
+      </c>
+      <c r="J32" t="n">
+        <v>66</v>
+      </c>
+      <c r="K32" t="n">
+        <v>60</v>
+      </c>
+      <c r="L32" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>72.183333</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>-2.121212</v>
+      </c>
+      <c r="P32" t="n">
+        <v>14.890713</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>96</v>
+      </c>
+      <c r="R32" t="n">
+        <v>51</v>
+      </c>
+      <c r="S32" t="n">
+        <v>28</v>
+      </c>
+      <c r="T32" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S032</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>72</v>
+      </c>
+      <c r="C33" t="n">
+        <v>83</v>
+      </c>
+      <c r="D33" t="n">
+        <v>64</v>
+      </c>
+      <c r="E33" t="n">
+        <v>74</v>
+      </c>
+      <c r="F33" t="n">
+        <v>77</v>
+      </c>
+      <c r="G33" t="n">
+        <v>64</v>
+      </c>
+      <c r="H33" t="n">
+        <v>62</v>
+      </c>
+      <c r="I33" t="n">
+        <v>75</v>
+      </c>
+      <c r="J33" t="n">
+        <v>85</v>
+      </c>
+      <c r="K33" t="n">
+        <v>66</v>
+      </c>
+      <c r="L33" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>-0.206061</v>
+      </c>
+      <c r="P33" t="n">
+        <v>8.107609999999999</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>85</v>
+      </c>
+      <c r="R33" t="n">
+        <v>62</v>
+      </c>
+      <c r="S33" t="n">
+        <v>29</v>
+      </c>
+      <c r="T33" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S033</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>66</v>
+      </c>
+      <c r="C34" t="n">
+        <v>73</v>
+      </c>
+      <c r="D34" t="n">
+        <v>78</v>
+      </c>
+      <c r="E34" t="n">
+        <v>68</v>
+      </c>
+      <c r="F34" t="n">
+        <v>70</v>
+      </c>
+      <c r="G34" t="n">
+        <v>71</v>
+      </c>
+      <c r="H34" t="n">
+        <v>60</v>
+      </c>
+      <c r="I34" t="n">
+        <v>72</v>
+      </c>
+      <c r="J34" t="n">
+        <v>67</v>
+      </c>
+      <c r="K34" t="n">
+        <v>95</v>
+      </c>
+      <c r="L34" t="n">
+        <v>72</v>
+      </c>
+      <c r="M34" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1.006061</v>
+      </c>
+      <c r="P34" t="n">
+        <v>9.380832</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>95</v>
+      </c>
+      <c r="R34" t="n">
+        <v>60</v>
+      </c>
+      <c r="S34" t="n">
+        <v>27</v>
+      </c>
+      <c r="T34" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="V34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S034</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>69</v>
+      </c>
+      <c r="C35" t="n">
+        <v>80</v>
+      </c>
+      <c r="D35" t="n">
+        <v>80</v>
+      </c>
+      <c r="E35" t="n">
+        <v>62</v>
+      </c>
+      <c r="F35" t="n">
+        <v>58</v>
+      </c>
+      <c r="G35" t="n">
+        <v>68</v>
+      </c>
+      <c r="H35" t="n">
+        <v>83</v>
+      </c>
+      <c r="I35" t="n">
+        <v>67</v>
+      </c>
+      <c r="J35" t="n">
+        <v>65</v>
+      </c>
+      <c r="K35" t="n">
+        <v>45</v>
+      </c>
+      <c r="L35" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="M35" t="n">
+        <v>66.016667</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>-1.89697</v>
+      </c>
+      <c r="P35" t="n">
+        <v>11.489609</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>83</v>
+      </c>
+      <c r="R35" t="n">
+        <v>45</v>
+      </c>
+      <c r="S35" t="n">
+        <v>39</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="V35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S035</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>70</v>
+      </c>
+      <c r="C36" t="n">
+        <v>79</v>
+      </c>
+      <c r="D36" t="n">
+        <v>80</v>
+      </c>
+      <c r="E36" t="n">
+        <v>80</v>
+      </c>
+      <c r="F36" t="n">
+        <v>70</v>
+      </c>
+      <c r="G36" t="n">
+        <v>71</v>
+      </c>
+      <c r="H36" t="n">
+        <v>85</v>
+      </c>
+      <c r="I36" t="n">
+        <v>72</v>
+      </c>
+      <c r="J36" t="n">
+        <v>45</v>
+      </c>
+      <c r="K36" t="n">
+        <v>87</v>
+      </c>
+      <c r="L36" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="M36" t="n">
+        <v>72.783333</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>-0.660606</v>
+      </c>
+      <c r="P36" t="n">
+        <v>11.892575</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>87</v>
+      </c>
+      <c r="R36" t="n">
+        <v>45</v>
+      </c>
+      <c r="S36" t="n">
+        <v>26</v>
+      </c>
+      <c r="T36" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S036</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>62</v>
+      </c>
+      <c r="C37" t="n">
+        <v>92</v>
+      </c>
+      <c r="D37" t="n">
+        <v>95</v>
+      </c>
+      <c r="E37" t="n">
+        <v>84</v>
+      </c>
+      <c r="F37" t="n">
+        <v>86</v>
+      </c>
+      <c r="G37" t="n">
+        <v>98</v>
+      </c>
+      <c r="H37" t="n">
+        <v>60</v>
+      </c>
+      <c r="I37" t="n">
+        <v>77</v>
+      </c>
+      <c r="J37" t="n">
+        <v>77</v>
+      </c>
+      <c r="K37" t="n">
+        <v>61</v>
+      </c>
+      <c r="L37" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>77.84999999999999</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="P37" t="n">
+        <v>14.304622</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>98</v>
+      </c>
+      <c r="R37" t="n">
+        <v>60</v>
+      </c>
+      <c r="S37" t="n">
+        <v>11</v>
+      </c>
+      <c r="T37" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="V37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S037</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>99</v>
+      </c>
+      <c r="C38" t="n">
+        <v>68</v>
+      </c>
+      <c r="D38" t="n">
+        <v>66</v>
+      </c>
+      <c r="E38" t="n">
+        <v>78</v>
+      </c>
+      <c r="F38" t="n">
+        <v>87</v>
+      </c>
+      <c r="G38" t="n">
+        <v>66</v>
+      </c>
+      <c r="H38" t="n">
+        <v>66</v>
+      </c>
+      <c r="I38" t="n">
+        <v>81</v>
+      </c>
+      <c r="J38" t="n">
+        <v>55</v>
+      </c>
+      <c r="K38" t="n">
+        <v>64</v>
+      </c>
+      <c r="L38" t="n">
+        <v>73</v>
+      </c>
+      <c r="M38" t="n">
+        <v>71.416667</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>-2.351515</v>
+      </c>
+      <c r="P38" t="n">
+        <v>13.072448</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>99</v>
+      </c>
+      <c r="R38" t="n">
+        <v>55</v>
+      </c>
+      <c r="S38" t="n">
+        <v>32</v>
+      </c>
+      <c r="T38" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="V38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S038</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>65</v>
+      </c>
+      <c r="C39" t="n">
+        <v>70</v>
+      </c>
+      <c r="D39" t="n">
+        <v>73</v>
+      </c>
+      <c r="E39" t="n">
+        <v>97</v>
+      </c>
+      <c r="F39" t="n">
+        <v>86</v>
+      </c>
+      <c r="G39" t="n">
+        <v>74</v>
+      </c>
+      <c r="H39" t="n">
+        <v>71</v>
+      </c>
+      <c r="I39" t="n">
+        <v>85</v>
+      </c>
+      <c r="J39" t="n">
+        <v>80</v>
+      </c>
+      <c r="K39" t="n">
+        <v>86</v>
+      </c>
+      <c r="L39" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="M39" t="n">
+        <v>79.516667</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>1.387879</v>
+      </c>
+      <c r="P39" t="n">
+        <v>9.775821000000001</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>97</v>
+      </c>
+      <c r="R39" t="n">
+        <v>65</v>
+      </c>
+      <c r="S39" t="n">
+        <v>7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="V39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S039</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>92</v>
+      </c>
+      <c r="C40" t="n">
+        <v>63</v>
+      </c>
+      <c r="D40" t="n">
         <v>48</v>
       </c>
-      <c r="F26" t="n">
-        <v>43</v>
-      </c>
-      <c r="G26" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.408319</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="E40" t="n">
+        <v>75</v>
+      </c>
+      <c r="F40" t="n">
+        <v>75</v>
+      </c>
+      <c r="G40" t="n">
+        <v>78</v>
+      </c>
+      <c r="H40" t="n">
+        <v>66</v>
+      </c>
+      <c r="I40" t="n">
+        <v>71</v>
+      </c>
+      <c r="J40" t="n">
+        <v>81</v>
+      </c>
+      <c r="K40" t="n">
+        <v>82</v>
+      </c>
+      <c r="L40" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M40" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0.769697</v>
+      </c>
+      <c r="P40" t="n">
+        <v>12.096372</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>92</v>
+      </c>
+      <c r="R40" t="n">
         <v>48</v>
       </c>
-      <c r="L26" t="n">
-        <v>42</v>
-      </c>
-      <c r="M26" t="n">
-        <v>25</v>
-      </c>
-      <c r="N26" t="b">
+      <c r="S40" t="n">
+        <v>21</v>
+      </c>
+      <c r="T40" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S040</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>91</v>
+      </c>
+      <c r="C41" t="n">
+        <v>49</v>
+      </c>
+      <c r="D41" t="n">
+        <v>55</v>
+      </c>
+      <c r="E41" t="n">
+        <v>93</v>
+      </c>
+      <c r="F41" t="n">
+        <v>82</v>
+      </c>
+      <c r="G41" t="n">
+        <v>84</v>
+      </c>
+      <c r="H41" t="n">
+        <v>70</v>
+      </c>
+      <c r="I41" t="n">
+        <v>68</v>
+      </c>
+      <c r="J41" t="n">
+        <v>77</v>
+      </c>
+      <c r="K41" t="n">
+        <v>62</v>
+      </c>
+      <c r="L41" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="M41" t="n">
+        <v>73.466667</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>-0.406061</v>
+      </c>
+      <c r="P41" t="n">
+        <v>14.895562</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>93</v>
+      </c>
+      <c r="R41" t="n">
+        <v>49</v>
+      </c>
+      <c r="S41" t="n">
+        <v>23</v>
+      </c>
+      <c r="T41" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="U41" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="V41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1701,13 +3422,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>assessment</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1734,96 +3455,191 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test1</t>
+          <t>quiz_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.88</v>
+        <v>75.8</v>
       </c>
       <c r="C2" t="n">
-        <v>16.202675</v>
+        <v>13.299701</v>
       </c>
       <c r="D2" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>test2</t>
+          <t>quiz_2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.12</v>
+        <v>73.52500000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>15.333297</v>
+        <v>12.571819</v>
       </c>
       <c r="D3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>test3</t>
+          <t>quiz_3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>74.55</v>
       </c>
       <c r="C4" t="n">
-        <v>16.114176</v>
+        <v>12.222195</v>
       </c>
       <c r="D4" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>test4</t>
+          <t>quiz_4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.92</v>
+        <v>75.77500000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>14.702381</v>
+        <v>11.618922</v>
       </c>
       <c r="D5" t="n">
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>test5</t>
+          <t>test_1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76.56</v>
+        <v>77.77500000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>16.835181</v>
+        <v>10.622877</v>
       </c>
       <c r="D6" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>test_2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14.01684</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>test_3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10.933834</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>test_4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12.307492</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>test_5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.555901</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>test_6</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>74.55</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14.103918</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1837,192 +3653,1731 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>quiz_1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>quiz_2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>quiz_3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>quiz_4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>test_1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>test_2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>test_3</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>test_4</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_5</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>test_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>class_average</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75.29600000000001</v>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>class_median</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77</v>
+        <v>0.62</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>grade_A+</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>-0.51</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>grade_A</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>-1.11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>grade_A-</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.09</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>grade_B+</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1.37</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>grade_B</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>-0.96</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>grade_B-</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-1.64</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>grade_C+</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1.29</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>grade_C</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0.47</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>grade_C-</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>-1.79</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>grade_D+</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>grade_D</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>0.92</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>grade_D-</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>-1.86</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>grade_F</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>1.29</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>most_improved_student</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S019</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S020</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S021</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S022</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S023</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S024</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S025</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S026</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S027</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S028</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S029</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S030</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S031</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S032</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S033</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S034</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S035</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S036</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S037</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S038</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S039</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S040</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>class_weighted_average</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>74.875833</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>class_median</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>75.033333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>grade_A+</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>grade_A</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>grade_A-</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>grade_B+</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>grade_B</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>grade_B-</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>grade_C+</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>grade_C</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>grade_C-</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>grade_D+</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>grade_D</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>grade_D-</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>grade_F</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>most_improved_student</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>most_consistent_student</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S004</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S021</t>
         </is>
       </c>
     </row>
